--- a/diseases/d085/2020-2025.xlsx
+++ b/diseases/d085/2020-2025.xlsx
@@ -913,9 +913,6 @@
       <c r="O3" t="n">
         <v>0</v>
       </c>
-      <c r="Q3" t="n">
-        <v>0</v>
-      </c>
       <c r="R3" t="n">
         <v>0</v>
       </c>
@@ -4267,9 +4264,6 @@
         <v>0</v>
       </c>
       <c r="O25" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q25" t="n">
         <v>0</v>
       </c>
       <c r="R25" t="n">
